--- a/Client/Configs/GameConfig/Datas/projectile.xlsx
+++ b/Client/Configs/GameConfig/Datas/projectile.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,43 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00000000"/>
-    </font>
-    <font>
-      <color rgb="007F6000"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -76,20 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -164,66 +122,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Codex</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>投射物表现表：只管飞行表现和特效资源，不决定伤害。</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>投射物ID。被 skill.xlsx 的 projectileId 引用。</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>投射物Key。程序/日志识别用。</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>飞行速度，单位米/秒。数值越大飞得越快。</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>命中半径，单位米。原型一般 0.2 到 0.5。</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>最大存活时间，单位秒。超过后自动销毁，避免特效残留。</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>飞行中特效Prefab路径。Blink资源先放在 ThirdParty 下引用。</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>出手/枪口/施法点特效Prefab路径。可以为空。</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>命中特效Prefab路径。可以为空。</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>Prefab加载失败时的备用颜色，HTML颜色格式，例如 #40C7FFFF。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -515,304 +413,317 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="92" customWidth="1" min="7" max="7"/>
-    <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="110" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>projectileKey</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>speed</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>hitRadius</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>maxLifetime</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>projectilePrefabPath</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>muzzlePrefabPath</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>impactPrefabPath</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>fallbackColor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>投射物ID。被 skill.xlsx 的 projectileId 引用。</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>投射物Key。程序/日志识别用。</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>飞行速度，单位米/秒。数值越大飞得越快。</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>命中半径，单位米。原型一般 0.2 到 0.5。</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>最大存活时间，单位秒。超过后自动销毁，避免特效残留。</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>飞行中特效Prefab路径。Blink资源先放在 ThirdParty 下引用。</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>出手/枪口/施法点特效Prefab路径。可以为空。</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>命中特效Prefab路径。可以为空。</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Prefab加载失败时的备用颜色，HTML颜色格式，例如 #40C7FFFF。</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Projectile id. 0 means none.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Projectile key.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Speed.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Hit radius.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Max lifetime.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Projectile prefab path.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Muzzle prefab path.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Impact prefab path.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fallback color.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n">
-        <v>300101</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>frostbolt_projectile</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/Art/CombatVisuals/Projectiles/Frostbolt.prefab</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/Art/CombatVisuals/Muzzle/FrostMuzzle.prefab</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/ThirdPartyAssets/GabrielAguiarProductions/Unique_Projectiles_Volume_2/Prefabs/Hits/vfx_Hit_IceSpike01_Blue.prefab</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>#40C7FFFF</t>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>#FFFFFFFF</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n">
+      <c r="B6" t="n">
+        <v>300101</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>frostbolt_projectile</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/Art/CombatVisuals/Projectiles/Frostbolt.prefab</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/Art/CombatVisuals/Muzzle/FrostMuzzle.prefab</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/ThirdPartyAssets/GabrielAguiarProductions/Unique_Projectiles_Volume_2/Prefabs/Hits/vfx_Hit_IceSpike01_Blue.prefab</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>#40C7FFFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
         <v>300102</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>fireball_projectile</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D7" t="n">
         <v>10</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E7" t="n">
         <v>0.25</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F7" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/Art/CombatVisuals/Projectiles/Fireball.prefab</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/Art/CombatVisuals/Muzzle/FireMuzzle.prefab</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/ThirdPartyAssets/GabrielAguiarProductions/Unique_Projectiles_Volume_2/Prefabs/Hits/vfx_Hit_Fireball04_Orange.prefab</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>#FF6114FF</t>
         </is>
@@ -820,6 +731,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/Client/Configs/GameConfig/Datas/projectile.xlsx
+++ b/Client/Configs/GameConfig/Datas/projectile.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,9 +642,6 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>#FFFFFFFF</t>
@@ -671,17 +668,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/Art/CombatVisuals/Projectiles/Frostbolt.prefab</t>
+          <t>Assets/AssetRaw/Effects/Skills/Frostbolt/Frostbolt.prefab</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/Art/CombatVisuals/Muzzle/FrostMuzzle.prefab</t>
+          <t>Assets/AssetRaw/Effects/Skills/Frostbolt/FrostMuzzle.prefab</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/ThirdPartyAssets/GabrielAguiarProductions/Unique_Projectiles_Volume_2/Prefabs/Hits/vfx_Hit_IceSpike01_Blue.prefab</t>
+          <t>Assets/AssetRaw/Effects/Skills/Frostbolt/vfx_Hit_IceSpike01_Blue.prefab</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -710,22 +707,201 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/Art/CombatVisuals/Projectiles/Fireball.prefab</t>
+          <t>Assets/AssetRaw/Effects/Skills/Fireball/Fireball.prefab</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/Art/CombatVisuals/Muzzle/FireMuzzle.prefab</t>
+          <t>Assets/AssetRaw/Effects/Skills/Fireball/FireMuzzle.prefab</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/ThirdPartyAssets/GabrielAguiarProductions/Unique_Projectiles_Volume_2/Prefabs/Hits/vfx_Hit_Fireball04_Orange.prefab</t>
+          <t>Assets/AssetRaw/Effects/Skills/Fireball/vfx_Hit_Fireball04_Orange.prefab</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>#FF6114FF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>300202</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>charge_impact</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Assets/AssetRaw/Effects/Skills/ThunderClap/ChargeStart_WarriorBuff.prefab</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Assets/AssetRaw/Effects/Skills/ThunderClap/ChargeImpact_Stun.prefab</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>#FFD36BFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>300203</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>thunder_clap_vfx</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Assets/AssetRaw/Effects/Skills/ThunderClap/Shockwave_URP.prefab</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>#FFD36BFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>300301</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>mage_basic_projectile</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Assets/AssetRaw/Effects/Skills/Frostbolt/vfx_Hit_IceSpike01_Blue.prefab</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>#B388FFFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>300401</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>priest_basic_projectile</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Assets/AssetRaw/Effects/Skills/Heal/Heal_Pulse.prefab</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>#FFECA3FF</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>300402</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>heal_pulse</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Assets/AssetRaw/Effects/Skills/Heal/Heal_Pulse.prefab</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>#66FFAAFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>300403</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>resurrection_placeholder</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Assets/ThirdParty/Blink/Tools/RPGBuilder/Art/VisualEffects/SkeletonHeal_Pulse.prefab</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>#F8F2D8FF</t>
         </is>
       </c>
     </row>
